--- a/old images/results/RealBenchmarkResults.xlsx
+++ b/old images/results/RealBenchmarkResults.xlsx
@@ -455,46 +455,46 @@
         <v>2.jpeg</v>
       </c>
       <c r="C2" t="str">
-        <v>NO</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
+        <v>YES</v>
+      </c>
+      <c r="D2" t="str">
+        <v>8748</v>
       </c>
       <c r="E2" t="str">
-        <v>0.000000</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+        <v>0.003400</v>
+      </c>
+      <c r="F2" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="G2" t="str">
+        <v>7.66</v>
+      </c>
+      <c r="H2" t="str">
+        <v>100</v>
+      </c>
+      <c r="I2" t="str">
+        <v>100</v>
+      </c>
+      <c r="J2" t="str">
+        <v>100</v>
+      </c>
+      <c r="K2" t="str">
+        <v>100</v>
+      </c>
+      <c r="L2" t="str">
+        <v>81</v>
       </c>
       <c r="M2" t="str">
         <v>525x380</v>
       </c>
       <c r="N2" t="str">
-        <v>0x0</v>
+        <v>1414x1024</v>
       </c>
       <c r="O2" t="str">
-        <v>Replicate API token not configured</v>
-      </c>
-    </row>
-    <row r="3">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>openai</v>
       </c>
@@ -504,31 +504,31 @@
       <c r="C3" t="str">
         <v>NO</v>
       </c>
-      <c r="D3">
-        <v>0</v>
+      <c r="D3" t="str">
+        <v>1966</v>
       </c>
       <c r="E3" t="str">
         <v>0.000000</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
+      <c r="F3" t="str">
+        <v>0</v>
+      </c>
+      <c r="G3" t="str">
+        <v>0</v>
+      </c>
+      <c r="H3" t="str">
+        <v>0</v>
+      </c>
+      <c r="I3" t="str">
+        <v>0</v>
+      </c>
+      <c r="J3" t="str">
+        <v>0</v>
+      </c>
+      <c r="K3" t="str">
+        <v>0</v>
+      </c>
+      <c r="L3" t="str">
         <v>0</v>
       </c>
       <c r="M3" t="str">
@@ -537,8 +537,15 @@
       <c r="N3" t="str">
         <v>0x0</v>
       </c>
-      <c r="O3" t="str">
-        <v>OpenAI API key not configured</v>
+      <c r="O3" t="str" xml:space="preserve">
+        <v xml:space="preserve">OpenAI API failed (400): {
+  "error": {
+    "message": "The model 'dall-e-3' does not exist.",
+    "type": "image_generation_user_error",
+    "param": "model",
+    "code": "invalid_value"
+  }
+}</v>
       </c>
     </row>
     <row r="4">
@@ -549,46 +556,46 @@
         <v>3.jpeg</v>
       </c>
       <c r="C4" t="str">
-        <v>NO</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
+        <v>YES</v>
+      </c>
+      <c r="D4" t="str">
+        <v>4712</v>
       </c>
       <c r="E4" t="str">
-        <v>0.000000</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+        <v>0.003400</v>
+      </c>
+      <c r="F4" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="G4" t="str">
+        <v>7.75</v>
+      </c>
+      <c r="H4" t="str">
+        <v>100</v>
+      </c>
+      <c r="I4" t="str">
+        <v>100</v>
+      </c>
+      <c r="J4" t="str">
+        <v>100</v>
+      </c>
+      <c r="K4" t="str">
+        <v>100</v>
+      </c>
+      <c r="L4" t="str">
+        <v>81</v>
       </c>
       <c r="M4" t="str">
         <v>455x673</v>
       </c>
       <c r="N4" t="str">
-        <v>0x0</v>
+        <v>1024x1514</v>
       </c>
       <c r="O4" t="str">
-        <v>Replicate API token not configured</v>
-      </c>
-    </row>
-    <row r="5">
+        <v/>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>openai</v>
       </c>
@@ -598,31 +605,31 @@
       <c r="C5" t="str">
         <v>NO</v>
       </c>
-      <c r="D5">
-        <v>0</v>
+      <c r="D5" t="str">
+        <v>850</v>
       </c>
       <c r="E5" t="str">
         <v>0.000000</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
+      <c r="F5" t="str">
+        <v>0</v>
+      </c>
+      <c r="G5" t="str">
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <v>0</v>
+      </c>
+      <c r="I5" t="str">
+        <v>0</v>
+      </c>
+      <c r="J5" t="str">
+        <v>0</v>
+      </c>
+      <c r="K5" t="str">
+        <v>0</v>
+      </c>
+      <c r="L5" t="str">
         <v>0</v>
       </c>
       <c r="M5" t="str">
@@ -631,8 +638,15 @@
       <c r="N5" t="str">
         <v>0x0</v>
       </c>
-      <c r="O5" t="str">
-        <v>OpenAI API key not configured</v>
+      <c r="O5" t="str" xml:space="preserve">
+        <v xml:space="preserve">OpenAI API failed (400): {
+  "error": {
+    "message": "The model 'dall-e-3' does not exist.",
+    "type": "image_generation_user_error",
+    "param": "model",
+    "code": "invalid_value"
+  }
+}</v>
       </c>
     </row>
     <row r="6">
@@ -643,46 +657,46 @@
         <v>4.jpg</v>
       </c>
       <c r="C6" t="str">
-        <v>NO</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
+        <v>YES</v>
+      </c>
+      <c r="D6" t="str">
+        <v>8684</v>
       </c>
       <c r="E6" t="str">
-        <v>0.000000</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
+        <v>0.003400</v>
+      </c>
+      <c r="F6" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="G6" t="str">
+        <v>7.65</v>
+      </c>
+      <c r="H6" t="str">
+        <v>100</v>
+      </c>
+      <c r="I6" t="str">
+        <v>100</v>
+      </c>
+      <c r="J6" t="str">
+        <v>100</v>
+      </c>
+      <c r="K6" t="str">
+        <v>100</v>
+      </c>
+      <c r="L6" t="str">
+        <v>81</v>
       </c>
       <c r="M6" t="str">
         <v>900x600</v>
       </c>
       <c r="N6" t="str">
-        <v>0x0</v>
+        <v>1800x1200</v>
       </c>
       <c r="O6" t="str">
-        <v>Replicate API token not configured</v>
-      </c>
-    </row>
-    <row r="7">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>openai</v>
       </c>
@@ -692,31 +706,31 @@
       <c r="C7" t="str">
         <v>NO</v>
       </c>
-      <c r="D7">
-        <v>1</v>
+      <c r="D7" t="str">
+        <v>2131</v>
       </c>
       <c r="E7" t="str">
         <v>0.000000</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
+      <c r="F7" t="str">
+        <v>0</v>
+      </c>
+      <c r="G7" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <v>0</v>
+      </c>
+      <c r="I7" t="str">
+        <v>0</v>
+      </c>
+      <c r="J7" t="str">
+        <v>0</v>
+      </c>
+      <c r="K7" t="str">
+        <v>0</v>
+      </c>
+      <c r="L7" t="str">
         <v>0</v>
       </c>
       <c r="M7" t="str">
@@ -725,8 +739,15 @@
       <c r="N7" t="str">
         <v>0x0</v>
       </c>
-      <c r="O7" t="str">
-        <v>OpenAI API key not configured</v>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">OpenAI API failed (400): {
+  "error": {
+    "message": "The model 'dall-e-3' does not exist.",
+    "type": "image_generation_user_error",
+    "param": "model",
+    "code": "invalid_value"
+  }
+}</v>
       </c>
     </row>
     <row r="8">
@@ -737,46 +758,46 @@
         <v>5.jpeg</v>
       </c>
       <c r="C8" t="str">
-        <v>NO</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
+        <v>YES</v>
+      </c>
+      <c r="D8" t="str">
+        <v>3964</v>
       </c>
       <c r="E8" t="str">
-        <v>0.000000</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
+        <v>0.003400</v>
+      </c>
+      <c r="F8" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="G8" t="str">
+        <v>7.64</v>
+      </c>
+      <c r="H8" t="str">
+        <v>100</v>
+      </c>
+      <c r="I8" t="str">
+        <v>100</v>
+      </c>
+      <c r="J8" t="str">
+        <v>100</v>
+      </c>
+      <c r="K8" t="str">
+        <v>100</v>
+      </c>
+      <c r="L8" t="str">
+        <v>81</v>
       </c>
       <c r="M8" t="str">
         <v>596x335</v>
       </c>
       <c r="N8" t="str">
-        <v>0x0</v>
+        <v>1822x1024</v>
       </c>
       <c r="O8" t="str">
-        <v>Replicate API token not configured</v>
-      </c>
-    </row>
-    <row r="9">
+        <v/>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
         <v>openai</v>
       </c>
@@ -786,31 +807,31 @@
       <c r="C9" t="str">
         <v>NO</v>
       </c>
-      <c r="D9">
-        <v>0</v>
+      <c r="D9" t="str">
+        <v>1853</v>
       </c>
       <c r="E9" t="str">
         <v>0.000000</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
+      <c r="F9" t="str">
+        <v>0</v>
+      </c>
+      <c r="G9" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9" t="str">
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <v>0</v>
+      </c>
+      <c r="J9" t="str">
+        <v>0</v>
+      </c>
+      <c r="K9" t="str">
+        <v>0</v>
+      </c>
+      <c r="L9" t="str">
         <v>0</v>
       </c>
       <c r="M9" t="str">
@@ -819,8 +840,15 @@
       <c r="N9" t="str">
         <v>0x0</v>
       </c>
-      <c r="O9" t="str">
-        <v>OpenAI API key not configured</v>
+      <c r="O9" t="str" xml:space="preserve">
+        <v xml:space="preserve">OpenAI API failed (400): {
+  "error": {
+    "message": "The model 'dall-e-3' does not exist.",
+    "type": "image_generation_user_error",
+    "param": "model",
+    "code": "invalid_value"
+  }
+}</v>
       </c>
     </row>
     <row r="10">
@@ -831,46 +859,46 @@
         <v>6.jpeg</v>
       </c>
       <c r="C10" t="str">
-        <v>NO</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
+        <v>YES</v>
+      </c>
+      <c r="D10" t="str">
+        <v>3543</v>
       </c>
       <c r="E10" t="str">
-        <v>0.000000</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
+        <v>0.003400</v>
+      </c>
+      <c r="F10" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="G10" t="str">
+        <v>7.77</v>
+      </c>
+      <c r="H10" t="str">
+        <v>100</v>
+      </c>
+      <c r="I10" t="str">
+        <v>100</v>
+      </c>
+      <c r="J10" t="str">
+        <v>100</v>
+      </c>
+      <c r="K10" t="str">
+        <v>100</v>
+      </c>
+      <c r="L10" t="str">
+        <v>81</v>
       </c>
       <c r="M10" t="str">
         <v>370x400</v>
       </c>
       <c r="N10" t="str">
-        <v>0x0</v>
+        <v>1024x1108</v>
       </c>
       <c r="O10" t="str">
-        <v>Replicate API token not configured</v>
-      </c>
-    </row>
-    <row r="11">
+        <v/>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
         <v>openai</v>
       </c>
@@ -880,31 +908,31 @@
       <c r="C11" t="str">
         <v>NO</v>
       </c>
-      <c r="D11">
-        <v>0</v>
+      <c r="D11" t="str">
+        <v>1881</v>
       </c>
       <c r="E11" t="str">
         <v>0.000000</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
+      <c r="F11" t="str">
+        <v>0</v>
+      </c>
+      <c r="G11" t="str">
+        <v>0</v>
+      </c>
+      <c r="H11" t="str">
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <v>0</v>
+      </c>
+      <c r="J11" t="str">
+        <v>0</v>
+      </c>
+      <c r="K11" t="str">
+        <v>0</v>
+      </c>
+      <c r="L11" t="str">
         <v>0</v>
       </c>
       <c r="M11" t="str">
@@ -913,8 +941,15 @@
       <c r="N11" t="str">
         <v>0x0</v>
       </c>
-      <c r="O11" t="str">
-        <v>OpenAI API key not configured</v>
+      <c r="O11" t="str" xml:space="preserve">
+        <v xml:space="preserve">OpenAI API failed (400): {
+  "error": {
+    "message": "The model 'dall-e-3' does not exist.",
+    "type": "image_generation_user_error",
+    "param": "model",
+    "code": "invalid_value"
+  }
+}</v>
       </c>
     </row>
     <row r="12">
@@ -925,46 +960,46 @@
         <v>images.jpeg</v>
       </c>
       <c r="C12" t="str">
-        <v>NO</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
+        <v>YES</v>
+      </c>
+      <c r="D12" t="str">
+        <v>4794</v>
       </c>
       <c r="E12" t="str">
-        <v>0.000000</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
+        <v>0.003400</v>
+      </c>
+      <c r="F12" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="G12" t="str">
+        <v>7.57</v>
+      </c>
+      <c r="H12" t="str">
+        <v>100</v>
+      </c>
+      <c r="I12" t="str">
+        <v>100</v>
+      </c>
+      <c r="J12" t="str">
+        <v>100</v>
+      </c>
+      <c r="K12" t="str">
+        <v>100</v>
+      </c>
+      <c r="L12" t="str">
+        <v>81</v>
       </c>
       <c r="M12" t="str">
         <v>493x405</v>
       </c>
       <c r="N12" t="str">
-        <v>0x0</v>
+        <v>1246x1024</v>
       </c>
       <c r="O12" t="str">
-        <v>Replicate API token not configured</v>
-      </c>
-    </row>
-    <row r="13">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>openai</v>
       </c>
@@ -974,31 +1009,31 @@
       <c r="C13" t="str">
         <v>NO</v>
       </c>
-      <c r="D13">
-        <v>0</v>
+      <c r="D13" t="str">
+        <v>902</v>
       </c>
       <c r="E13" t="str">
         <v>0.000000</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
+      <c r="F13" t="str">
+        <v>0</v>
+      </c>
+      <c r="G13" t="str">
+        <v>0</v>
+      </c>
+      <c r="H13" t="str">
+        <v>0</v>
+      </c>
+      <c r="I13" t="str">
+        <v>0</v>
+      </c>
+      <c r="J13" t="str">
+        <v>0</v>
+      </c>
+      <c r="K13" t="str">
+        <v>0</v>
+      </c>
+      <c r="L13" t="str">
         <v>0</v>
       </c>
       <c r="M13" t="str">
@@ -1007,8 +1042,15 @@
       <c r="N13" t="str">
         <v>0x0</v>
       </c>
-      <c r="O13" t="str">
-        <v>OpenAI API key not configured</v>
+      <c r="O13" t="str" xml:space="preserve">
+        <v xml:space="preserve">OpenAI API failed (400): {
+  "error": {
+    "message": "The model 'dall-e-3' does not exist.",
+    "type": "image_generation_user_error",
+    "param": "model",
+    "code": "invalid_value"
+  }
+}</v>
       </c>
     </row>
     <row r="14">
@@ -1019,46 +1061,46 @@
         <v>lahore.jpeg</v>
       </c>
       <c r="C14" t="str">
-        <v>NO</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
+        <v>YES</v>
+      </c>
+      <c r="D14" t="str">
+        <v>3417</v>
       </c>
       <c r="E14" t="str">
-        <v>0.000000</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
+        <v>0.003400</v>
+      </c>
+      <c r="F14" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="G14" t="str">
+        <v>7.62</v>
+      </c>
+      <c r="H14" t="str">
+        <v>100</v>
+      </c>
+      <c r="I14" t="str">
+        <v>100</v>
+      </c>
+      <c r="J14" t="str">
+        <v>100</v>
+      </c>
+      <c r="K14" t="str">
+        <v>100</v>
+      </c>
+      <c r="L14" t="str">
+        <v>81</v>
       </c>
       <c r="M14" t="str">
         <v>502x611</v>
       </c>
       <c r="N14" t="str">
-        <v>0x0</v>
+        <v>1024x1246</v>
       </c>
       <c r="O14" t="str">
-        <v>Replicate API token not configured</v>
-      </c>
-    </row>
-    <row r="15">
+        <v/>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
       <c r="A15" t="str">
         <v>openai</v>
       </c>
@@ -1068,31 +1110,31 @@
       <c r="C15" t="str">
         <v>NO</v>
       </c>
-      <c r="D15">
-        <v>0</v>
+      <c r="D15" t="str">
+        <v>1994</v>
       </c>
       <c r="E15" t="str">
         <v>0.000000</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
+      <c r="F15" t="str">
+        <v>0</v>
+      </c>
+      <c r="G15" t="str">
+        <v>0</v>
+      </c>
+      <c r="H15" t="str">
+        <v>0</v>
+      </c>
+      <c r="I15" t="str">
+        <v>0</v>
+      </c>
+      <c r="J15" t="str">
+        <v>0</v>
+      </c>
+      <c r="K15" t="str">
+        <v>0</v>
+      </c>
+      <c r="L15" t="str">
         <v>0</v>
       </c>
       <c r="M15" t="str">
@@ -1101,8 +1143,15 @@
       <c r="N15" t="str">
         <v>0x0</v>
       </c>
-      <c r="O15" t="str">
-        <v>OpenAI API key not configured</v>
+      <c r="O15" t="str" xml:space="preserve">
+        <v xml:space="preserve">OpenAI API failed (400): {
+  "error": {
+    "message": "The model 'dall-e-3' does not exist.",
+    "type": "image_generation_user_error",
+    "param": "model",
+    "code": "invalid_value"
+  }
+}</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1181,7 @@
         <v>Processed</v>
       </c>
       <c r="B2" t="str">
-        <v>0/7</v>
+        <v>7/7</v>
       </c>
       <c r="C2" t="str">
         <v>0/7</v>
@@ -1143,7 +1192,7 @@
         <v>Avg Cost/Image</v>
       </c>
       <c r="B3" t="str">
-        <v>0.000000</v>
+        <v>0.003400</v>
       </c>
       <c r="C3" t="str">
         <v>0.000000</v>
@@ -1154,7 +1203,7 @@
         <v>Total Cost</v>
       </c>
       <c r="B4" t="str">
-        <v>0.000000</v>
+        <v>0.023800</v>
       </c>
       <c r="C4" t="str">
         <v>0.000000</v>
@@ -1165,7 +1214,7 @@
         <v>Avg Latency (ms)</v>
       </c>
       <c r="B5" t="str">
-        <v>0</v>
+        <v>5409</v>
       </c>
       <c r="C5" t="str">
         <v>0</v>
@@ -1176,7 +1225,7 @@
         <v>Avg SSIM</v>
       </c>
       <c r="B6" t="str">
-        <v>0.00</v>
+        <v>0.80</v>
       </c>
       <c r="C6" t="str">
         <v>0.00</v>
@@ -1187,7 +1236,7 @@
         <v>Avg PSNR</v>
       </c>
       <c r="B7" t="str">
-        <v>0.00</v>
+        <v>7.67</v>
       </c>
       <c r="C7" t="str">
         <v>0.00</v>

--- a/old images/results/RealBenchmarkResults.xlsx
+++ b/old images/results/RealBenchmarkResults.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:S15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,36 +414,48 @@
         <v>Elapsed (ms)</v>
       </c>
       <c r="E1" t="str">
-        <v>Cost ($)</v>
+        <v>Actual Cost ($)</v>
       </c>
       <c r="F1" t="str">
+        <v>Est. Cost ($)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Cost Source</v>
+      </c>
+      <c r="H1" t="str">
+        <v>GPU Secs</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Request ID</v>
+      </c>
+      <c r="J1" t="str">
         <v>SSIM</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>PSNR</v>
       </c>
-      <c r="H1" t="str">
+      <c r="L1" t="str">
         <v>Sharpness</v>
       </c>
-      <c r="I1" t="str">
+      <c r="M1" t="str">
         <v>Noise</v>
       </c>
-      <c r="J1" t="str">
+      <c r="N1" t="str">
         <v>Contrast</v>
       </c>
-      <c r="K1" t="str">
+      <c r="O1" t="str">
         <v>Brightness</v>
       </c>
-      <c r="L1" t="str">
+      <c r="P1" t="str">
         <v>Print Quality</v>
       </c>
-      <c r="M1" t="str">
+      <c r="Q1" t="str">
         <v>Input WxH</v>
       </c>
-      <c r="N1" t="str">
+      <c r="R1" t="str">
         <v>Output WxH</v>
       </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
         <v>Failure Reason</v>
       </c>
     </row>
@@ -458,43 +470,55 @@
         <v>YES</v>
       </c>
       <c r="D2" t="str">
-        <v>8748</v>
+        <v>7903</v>
       </c>
       <c r="E2" t="str">
+        <v>0.001900</v>
+      </c>
+      <c r="F2" t="str">
         <v>0.003400</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v>calculated</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2.185350542</v>
+      </c>
+      <c r="I2" t="str">
+        <v>rh0ada5xcnrmw0czh7jvvtxr2w</v>
+      </c>
+      <c r="J2" t="str">
         <v>0.8</v>
       </c>
-      <c r="G2" t="str">
+      <c r="K2" t="str">
         <v>7.66</v>
       </c>
-      <c r="H2" t="str">
-        <v>100</v>
-      </c>
-      <c r="I2" t="str">
-        <v>100</v>
-      </c>
-      <c r="J2" t="str">
-        <v>100</v>
-      </c>
-      <c r="K2" t="str">
-        <v>100</v>
-      </c>
       <c r="L2" t="str">
+        <v>100</v>
+      </c>
+      <c r="M2" t="str">
+        <v>100</v>
+      </c>
+      <c r="N2" t="str">
+        <v>100</v>
+      </c>
+      <c r="O2" t="str">
+        <v>100</v>
+      </c>
+      <c r="P2" t="str">
         <v>81</v>
       </c>
-      <c r="M2" t="str">
+      <c r="Q2" t="str">
         <v>525x380</v>
       </c>
-      <c r="N2" t="str">
+      <c r="R2" t="str">
         <v>1414x1024</v>
       </c>
-      <c r="O2" t="str">
+      <c r="S2" t="str">
         <v/>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
         <v>openai</v>
       </c>
@@ -502,50 +526,55 @@
         <v>2.jpeg</v>
       </c>
       <c r="C3" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="D3" t="str">
-        <v>1966</v>
+        <v>53544</v>
       </c>
       <c r="E3" t="str">
-        <v>0.000000</v>
+        <v>0.000070</v>
       </c>
       <c r="F3" t="str">
-        <v>0</v>
+        <v>0.040000</v>
       </c>
       <c r="G3" t="str">
-        <v>0</v>
+        <v>actual</v>
       </c>
       <c r="H3" t="str">
         <v>0</v>
       </c>
       <c r="I3" t="str">
-        <v>0</v>
+        <v>1784725023</v>
       </c>
       <c r="J3" t="str">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="str">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" t="str">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M3" t="str">
+        <v>100</v>
+      </c>
+      <c r="N3" t="str">
+        <v>100</v>
+      </c>
+      <c r="O3" t="str">
+        <v>100</v>
+      </c>
+      <c r="P3" t="str">
+        <v>81</v>
+      </c>
+      <c r="Q3" t="str">
         <v>525x380</v>
       </c>
-      <c r="N3" t="str">
-        <v>0x0</v>
-      </c>
-      <c r="O3" t="str" xml:space="preserve">
-        <v xml:space="preserve">OpenAI API failed (400): {
-  "error": {
-    "message": "The model 'dall-e-3' does not exist.",
-    "type": "image_generation_user_error",
-    "param": "model",
-    "code": "invalid_value"
-  }
-}</v>
+      <c r="R3" t="str">
+        <v>1024x1024</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -559,43 +588,55 @@
         <v>YES</v>
       </c>
       <c r="D4" t="str">
-        <v>4712</v>
+        <v>5116</v>
       </c>
       <c r="E4" t="str">
+        <v>0.001700</v>
+      </c>
+      <c r="F4" t="str">
         <v>0.003400</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v>calculated</v>
+      </c>
+      <c r="H4" t="str">
+        <v>1.999089495</v>
+      </c>
+      <c r="I4" t="str">
+        <v>jr6f5vxzrhrmr0czh7k9xc6per</v>
+      </c>
+      <c r="J4" t="str">
         <v>0.8</v>
       </c>
-      <c r="G4" t="str">
+      <c r="K4" t="str">
         <v>7.75</v>
       </c>
-      <c r="H4" t="str">
-        <v>100</v>
-      </c>
-      <c r="I4" t="str">
-        <v>100</v>
-      </c>
-      <c r="J4" t="str">
-        <v>100</v>
-      </c>
-      <c r="K4" t="str">
-        <v>100</v>
-      </c>
       <c r="L4" t="str">
+        <v>100</v>
+      </c>
+      <c r="M4" t="str">
+        <v>100</v>
+      </c>
+      <c r="N4" t="str">
+        <v>100</v>
+      </c>
+      <c r="O4" t="str">
+        <v>100</v>
+      </c>
+      <c r="P4" t="str">
         <v>81</v>
       </c>
-      <c r="M4" t="str">
+      <c r="Q4" t="str">
         <v>455x673</v>
       </c>
-      <c r="N4" t="str">
+      <c r="R4" t="str">
         <v>1024x1514</v>
       </c>
-      <c r="O4" t="str">
+      <c r="S4" t="str">
         <v/>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
         <v>openai</v>
       </c>
@@ -603,50 +644,55 @@
         <v>3.jpeg</v>
       </c>
       <c r="C5" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="D5" t="str">
-        <v>850</v>
+        <v>30414</v>
       </c>
       <c r="E5" t="str">
-        <v>0.000000</v>
+        <v>0.000070</v>
       </c>
       <c r="F5" t="str">
-        <v>0</v>
+        <v>0.040000</v>
       </c>
       <c r="G5" t="str">
-        <v>0</v>
+        <v>actual</v>
       </c>
       <c r="H5" t="str">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>0</v>
+        <v>1784725065</v>
       </c>
       <c r="J5" t="str">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="str">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="L5" t="str">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5" t="str">
+        <v>100</v>
+      </c>
+      <c r="N5" t="str">
+        <v>100</v>
+      </c>
+      <c r="O5" t="str">
+        <v>100</v>
+      </c>
+      <c r="P5" t="str">
+        <v>81</v>
+      </c>
+      <c r="Q5" t="str">
         <v>455x673</v>
       </c>
-      <c r="N5" t="str">
-        <v>0x0</v>
-      </c>
-      <c r="O5" t="str" xml:space="preserve">
-        <v xml:space="preserve">OpenAI API failed (400): {
-  "error": {
-    "message": "The model 'dall-e-3' does not exist.",
-    "type": "image_generation_user_error",
-    "param": "model",
-    "code": "invalid_value"
-  }
-}</v>
+      <c r="R5" t="str">
+        <v>1024x1024</v>
+      </c>
+      <c r="S5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -660,43 +706,55 @@
         <v>YES</v>
       </c>
       <c r="D6" t="str">
-        <v>8684</v>
+        <v>7961</v>
       </c>
       <c r="E6" t="str">
+        <v>0.003600</v>
+      </c>
+      <c r="F6" t="str">
         <v>0.003400</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
+        <v>calculated</v>
+      </c>
+      <c r="H6" t="str">
+        <v>4.207488924</v>
+      </c>
+      <c r="I6" t="str">
+        <v>r9baz8v3pdrmr0czh7ksbffws8</v>
+      </c>
+      <c r="J6" t="str">
         <v>0.8</v>
       </c>
-      <c r="G6" t="str">
+      <c r="K6" t="str">
         <v>7.65</v>
       </c>
-      <c r="H6" t="str">
-        <v>100</v>
-      </c>
-      <c r="I6" t="str">
-        <v>100</v>
-      </c>
-      <c r="J6" t="str">
-        <v>100</v>
-      </c>
-      <c r="K6" t="str">
-        <v>100</v>
-      </c>
       <c r="L6" t="str">
+        <v>100</v>
+      </c>
+      <c r="M6" t="str">
+        <v>100</v>
+      </c>
+      <c r="N6" t="str">
+        <v>100</v>
+      </c>
+      <c r="O6" t="str">
+        <v>100</v>
+      </c>
+      <c r="P6" t="str">
         <v>81</v>
       </c>
-      <c r="M6" t="str">
+      <c r="Q6" t="str">
         <v>900x600</v>
       </c>
-      <c r="N6" t="str">
+      <c r="R6" t="str">
         <v>1800x1200</v>
       </c>
-      <c r="O6" t="str">
+      <c r="S6" t="str">
         <v/>
       </c>
     </row>
-    <row r="7" xml:space="preserve">
+    <row r="7">
       <c r="A7" t="str">
         <v>openai</v>
       </c>
@@ -704,50 +762,55 @@
         <v>4.jpg</v>
       </c>
       <c r="C7" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="D7" t="str">
-        <v>2131</v>
+        <v>34462</v>
       </c>
       <c r="E7" t="str">
-        <v>0.000000</v>
+        <v>0.000070</v>
       </c>
       <c r="F7" t="str">
-        <v>0</v>
+        <v>0.040000</v>
       </c>
       <c r="G7" t="str">
-        <v>0</v>
+        <v>actual</v>
       </c>
       <c r="H7" t="str">
         <v>0</v>
       </c>
       <c r="I7" t="str">
-        <v>0</v>
+        <v>1784725114</v>
       </c>
       <c r="J7" t="str">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="str">
-        <v>0</v>
+        <v>7.74</v>
       </c>
       <c r="L7" t="str">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7" t="str">
+        <v>100</v>
+      </c>
+      <c r="N7" t="str">
+        <v>100</v>
+      </c>
+      <c r="O7" t="str">
+        <v>100</v>
+      </c>
+      <c r="P7" t="str">
+        <v>81</v>
+      </c>
+      <c r="Q7" t="str">
         <v>900x600</v>
       </c>
-      <c r="N7" t="str">
-        <v>0x0</v>
-      </c>
-      <c r="O7" t="str" xml:space="preserve">
-        <v xml:space="preserve">OpenAI API failed (400): {
-  "error": {
-    "message": "The model 'dall-e-3' does not exist.",
-    "type": "image_generation_user_error",
-    "param": "model",
-    "code": "invalid_value"
-  }
-}</v>
+      <c r="R7" t="str">
+        <v>1024x1024</v>
+      </c>
+      <c r="S7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -761,43 +824,55 @@
         <v>YES</v>
       </c>
       <c r="D8" t="str">
-        <v>3964</v>
+        <v>6156</v>
       </c>
       <c r="E8" t="str">
+        <v>0.002500</v>
+      </c>
+      <c r="F8" t="str">
         <v>0.003400</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
+        <v>calculated</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2.998366182</v>
+      </c>
+      <c r="I8" t="str">
+        <v>hwy8vc8zqdrmw0czh7m9xdzp14</v>
+      </c>
+      <c r="J8" t="str">
         <v>0.8</v>
       </c>
-      <c r="G8" t="str">
+      <c r="K8" t="str">
         <v>7.64</v>
       </c>
-      <c r="H8" t="str">
-        <v>100</v>
-      </c>
-      <c r="I8" t="str">
-        <v>100</v>
-      </c>
-      <c r="J8" t="str">
-        <v>100</v>
-      </c>
-      <c r="K8" t="str">
-        <v>100</v>
-      </c>
       <c r="L8" t="str">
+        <v>100</v>
+      </c>
+      <c r="M8" t="str">
+        <v>100</v>
+      </c>
+      <c r="N8" t="str">
+        <v>100</v>
+      </c>
+      <c r="O8" t="str">
+        <v>100</v>
+      </c>
+      <c r="P8" t="str">
         <v>81</v>
       </c>
-      <c r="M8" t="str">
+      <c r="Q8" t="str">
         <v>596x335</v>
       </c>
-      <c r="N8" t="str">
+      <c r="R8" t="str">
         <v>1822x1024</v>
       </c>
-      <c r="O8" t="str">
+      <c r="S8" t="str">
         <v/>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
+    <row r="9">
       <c r="A9" t="str">
         <v>openai</v>
       </c>
@@ -805,50 +880,55 @@
         <v>5.jpeg</v>
       </c>
       <c r="C9" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="D9" t="str">
-        <v>1853</v>
+        <v>35055</v>
       </c>
       <c r="E9" t="str">
-        <v>0.000000</v>
+        <v>0.000070</v>
       </c>
       <c r="F9" t="str">
-        <v>0</v>
+        <v>0.040000</v>
       </c>
       <c r="G9" t="str">
-        <v>0</v>
+        <v>actual</v>
       </c>
       <c r="H9" t="str">
         <v>0</v>
       </c>
       <c r="I9" t="str">
-        <v>0</v>
+        <v>1784725160</v>
       </c>
       <c r="J9" t="str">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="str">
-        <v>0</v>
+        <v>6.69</v>
       </c>
       <c r="L9" t="str">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M9" t="str">
+        <v>100</v>
+      </c>
+      <c r="N9" t="str">
+        <v>100</v>
+      </c>
+      <c r="O9" t="str">
+        <v>100</v>
+      </c>
+      <c r="P9" t="str">
+        <v>81</v>
+      </c>
+      <c r="Q9" t="str">
         <v>596x335</v>
       </c>
-      <c r="N9" t="str">
-        <v>0x0</v>
-      </c>
-      <c r="O9" t="str" xml:space="preserve">
-        <v xml:space="preserve">OpenAI API failed (400): {
-  "error": {
-    "message": "The model 'dall-e-3' does not exist.",
-    "type": "image_generation_user_error",
-    "param": "model",
-    "code": "invalid_value"
-  }
-}</v>
+      <c r="R9" t="str">
+        <v>1024x1024</v>
+      </c>
+      <c r="S9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -862,43 +942,55 @@
         <v>YES</v>
       </c>
       <c r="D10" t="str">
-        <v>3543</v>
+        <v>4995</v>
       </c>
       <c r="E10" t="str">
+        <v>0.001100</v>
+      </c>
+      <c r="F10" t="str">
         <v>0.003400</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
+        <v>calculated</v>
+      </c>
+      <c r="H10" t="str">
+        <v>1.250076669</v>
+      </c>
+      <c r="I10" t="str">
+        <v>4mpvrgypvxrmy0czh7ma932p6r</v>
+      </c>
+      <c r="J10" t="str">
         <v>0.8</v>
       </c>
-      <c r="G10" t="str">
+      <c r="K10" t="str">
         <v>7.77</v>
       </c>
-      <c r="H10" t="str">
-        <v>100</v>
-      </c>
-      <c r="I10" t="str">
-        <v>100</v>
-      </c>
-      <c r="J10" t="str">
-        <v>100</v>
-      </c>
-      <c r="K10" t="str">
-        <v>100</v>
-      </c>
       <c r="L10" t="str">
+        <v>100</v>
+      </c>
+      <c r="M10" t="str">
+        <v>100</v>
+      </c>
+      <c r="N10" t="str">
+        <v>100</v>
+      </c>
+      <c r="O10" t="str">
+        <v>100</v>
+      </c>
+      <c r="P10" t="str">
         <v>81</v>
       </c>
-      <c r="M10" t="str">
+      <c r="Q10" t="str">
         <v>370x400</v>
       </c>
-      <c r="N10" t="str">
+      <c r="R10" t="str">
         <v>1024x1108</v>
       </c>
-      <c r="O10" t="str">
+      <c r="S10" t="str">
         <v/>
       </c>
     </row>
-    <row r="11" xml:space="preserve">
+    <row r="11">
       <c r="A11" t="str">
         <v>openai</v>
       </c>
@@ -906,50 +998,55 @@
         <v>6.jpeg</v>
       </c>
       <c r="C11" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="D11" t="str">
-        <v>1881</v>
+        <v>36727</v>
       </c>
       <c r="E11" t="str">
-        <v>0.000000</v>
+        <v>0.000070</v>
       </c>
       <c r="F11" t="str">
-        <v>0</v>
+        <v>0.040000</v>
       </c>
       <c r="G11" t="str">
-        <v>0</v>
+        <v>actual</v>
       </c>
       <c r="H11" t="str">
         <v>0</v>
       </c>
       <c r="I11" t="str">
-        <v>0</v>
+        <v>1784725208</v>
       </c>
       <c r="J11" t="str">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="str">
-        <v>0</v>
+        <v>7.23</v>
       </c>
       <c r="L11" t="str">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11" t="str">
+        <v>100</v>
+      </c>
+      <c r="N11" t="str">
+        <v>100</v>
+      </c>
+      <c r="O11" t="str">
+        <v>100</v>
+      </c>
+      <c r="P11" t="str">
+        <v>81</v>
+      </c>
+      <c r="Q11" t="str">
         <v>370x400</v>
       </c>
-      <c r="N11" t="str">
-        <v>0x0</v>
-      </c>
-      <c r="O11" t="str" xml:space="preserve">
-        <v xml:space="preserve">OpenAI API failed (400): {
-  "error": {
-    "message": "The model 'dall-e-3' does not exist.",
-    "type": "image_generation_user_error",
-    "param": "model",
-    "code": "invalid_value"
-  }
-}</v>
+      <c r="R11" t="str">
+        <v>1024x1024</v>
+      </c>
+      <c r="S11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -963,43 +1060,55 @@
         <v>YES</v>
       </c>
       <c r="D12" t="str">
-        <v>4794</v>
+        <v>7235</v>
       </c>
       <c r="E12" t="str">
+        <v>0.003800</v>
+      </c>
+      <c r="F12" t="str">
         <v>0.003400</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
+        <v>calculated</v>
+      </c>
+      <c r="H12" t="str">
+        <v>4.45141675</v>
+      </c>
+      <c r="I12" t="str">
+        <v>6xg7r9mjjhrmw0czh7mv127byr</v>
+      </c>
+      <c r="J12" t="str">
         <v>0.8</v>
       </c>
-      <c r="G12" t="str">
+      <c r="K12" t="str">
         <v>7.57</v>
       </c>
-      <c r="H12" t="str">
-        <v>100</v>
-      </c>
-      <c r="I12" t="str">
-        <v>100</v>
-      </c>
-      <c r="J12" t="str">
-        <v>100</v>
-      </c>
-      <c r="K12" t="str">
-        <v>100</v>
-      </c>
       <c r="L12" t="str">
+        <v>100</v>
+      </c>
+      <c r="M12" t="str">
+        <v>100</v>
+      </c>
+      <c r="N12" t="str">
+        <v>100</v>
+      </c>
+      <c r="O12" t="str">
+        <v>100</v>
+      </c>
+      <c r="P12" t="str">
         <v>81</v>
       </c>
-      <c r="M12" t="str">
+      <c r="Q12" t="str">
         <v>493x405</v>
       </c>
-      <c r="N12" t="str">
+      <c r="R12" t="str">
         <v>1246x1024</v>
       </c>
-      <c r="O12" t="str">
+      <c r="S12" t="str">
         <v/>
       </c>
     </row>
-    <row r="13" xml:space="preserve">
+    <row r="13">
       <c r="A13" t="str">
         <v>openai</v>
       </c>
@@ -1007,50 +1116,55 @@
         <v>images.jpeg</v>
       </c>
       <c r="C13" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="D13" t="str">
-        <v>902</v>
+        <v>36656</v>
       </c>
       <c r="E13" t="str">
-        <v>0.000000</v>
+        <v>0.000070</v>
       </c>
       <c r="F13" t="str">
-        <v>0</v>
+        <v>0.040000</v>
       </c>
       <c r="G13" t="str">
-        <v>0</v>
+        <v>actual</v>
       </c>
       <c r="H13" t="str">
         <v>0</v>
       </c>
       <c r="I13" t="str">
-        <v>0</v>
+        <v>1784725259</v>
       </c>
       <c r="J13" t="str">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="str">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="L13" t="str">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13" t="str">
+        <v>100</v>
+      </c>
+      <c r="N13" t="str">
+        <v>100</v>
+      </c>
+      <c r="O13" t="str">
+        <v>100</v>
+      </c>
+      <c r="P13" t="str">
+        <v>81</v>
+      </c>
+      <c r="Q13" t="str">
         <v>493x405</v>
       </c>
-      <c r="N13" t="str">
-        <v>0x0</v>
-      </c>
-      <c r="O13" t="str" xml:space="preserve">
-        <v xml:space="preserve">OpenAI API failed (400): {
-  "error": {
-    "message": "The model 'dall-e-3' does not exist.",
-    "type": "image_generation_user_error",
-    "param": "model",
-    "code": "invalid_value"
-  }
-}</v>
+      <c r="R13" t="str">
+        <v>1024x1024</v>
+      </c>
+      <c r="S13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1064,43 +1178,55 @@
         <v>YES</v>
       </c>
       <c r="D14" t="str">
-        <v>3417</v>
+        <v>5304</v>
       </c>
       <c r="E14" t="str">
+        <v>0.000800</v>
+      </c>
+      <c r="F14" t="str">
         <v>0.003400</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
+        <v>calculated</v>
+      </c>
+      <c r="H14" t="str">
+        <v>0.965610983</v>
+      </c>
+      <c r="I14" t="str">
+        <v>pyp2akatn5rmy0czh7n9cbj73w</v>
+      </c>
+      <c r="J14" t="str">
         <v>0.8</v>
       </c>
-      <c r="G14" t="str">
+      <c r="K14" t="str">
         <v>7.62</v>
       </c>
-      <c r="H14" t="str">
-        <v>100</v>
-      </c>
-      <c r="I14" t="str">
-        <v>100</v>
-      </c>
-      <c r="J14" t="str">
-        <v>100</v>
-      </c>
-      <c r="K14" t="str">
-        <v>100</v>
-      </c>
       <c r="L14" t="str">
+        <v>100</v>
+      </c>
+      <c r="M14" t="str">
+        <v>100</v>
+      </c>
+      <c r="N14" t="str">
+        <v>100</v>
+      </c>
+      <c r="O14" t="str">
+        <v>100</v>
+      </c>
+      <c r="P14" t="str">
         <v>81</v>
       </c>
-      <c r="M14" t="str">
+      <c r="Q14" t="str">
         <v>502x611</v>
       </c>
-      <c r="N14" t="str">
+      <c r="R14" t="str">
         <v>1024x1246</v>
       </c>
-      <c r="O14" t="str">
+      <c r="S14" t="str">
         <v/>
       </c>
     </row>
-    <row r="15" xml:space="preserve">
+    <row r="15">
       <c r="A15" t="str">
         <v>openai</v>
       </c>
@@ -1108,55 +1234,60 @@
         <v>lahore.jpeg</v>
       </c>
       <c r="C15" t="str">
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="D15" t="str">
-        <v>1994</v>
+        <v>46307</v>
       </c>
       <c r="E15" t="str">
-        <v>0.000000</v>
+        <v>0.000070</v>
       </c>
       <c r="F15" t="str">
-        <v>0</v>
+        <v>0.040000</v>
       </c>
       <c r="G15" t="str">
-        <v>0</v>
+        <v>actual</v>
       </c>
       <c r="H15" t="str">
         <v>0</v>
       </c>
       <c r="I15" t="str">
-        <v>0</v>
+        <v>1784725316</v>
       </c>
       <c r="J15" t="str">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K15" t="str">
-        <v>0</v>
+        <v>7.04</v>
       </c>
       <c r="L15" t="str">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" t="str">
+        <v>100</v>
+      </c>
+      <c r="N15" t="str">
+        <v>100</v>
+      </c>
+      <c r="O15" t="str">
+        <v>100</v>
+      </c>
+      <c r="P15" t="str">
+        <v>81</v>
+      </c>
+      <c r="Q15" t="str">
         <v>502x611</v>
       </c>
-      <c r="N15" t="str">
-        <v>0x0</v>
-      </c>
-      <c r="O15" t="str" xml:space="preserve">
-        <v xml:space="preserve">OpenAI API failed (400): {
-  "error": {
-    "message": "The model 'dall-e-3' does not exist.",
-    "type": "image_generation_user_error",
-    "param": "model",
-    "code": "invalid_value"
-  }
-}</v>
+      <c r="R15" t="str">
+        <v>1024x1024</v>
+      </c>
+      <c r="S15" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1184,7 +1315,7 @@
         <v>7/7</v>
       </c>
       <c r="C2" t="str">
-        <v>0/7</v>
+        <v>7/7</v>
       </c>
     </row>
     <row r="3">
@@ -1192,10 +1323,10 @@
         <v>Avg Cost/Image</v>
       </c>
       <c r="B3" t="str">
-        <v>0.003400</v>
+        <v>0.002200</v>
       </c>
       <c r="C3" t="str">
-        <v>0.000000</v>
+        <v>0.000070</v>
       </c>
     </row>
     <row r="4">
@@ -1203,10 +1334,10 @@
         <v>Total Cost</v>
       </c>
       <c r="B4" t="str">
-        <v>0.023800</v>
+        <v>0.015400</v>
       </c>
       <c r="C4" t="str">
-        <v>0.000000</v>
+        <v>0.000490</v>
       </c>
     </row>
     <row r="5">
@@ -1214,10 +1345,10 @@
         <v>Avg Latency (ms)</v>
       </c>
       <c r="B5" t="str">
-        <v>5409</v>
+        <v>6381</v>
       </c>
       <c r="C5" t="str">
-        <v>0</v>
+        <v>39024</v>
       </c>
     </row>
     <row r="6">
@@ -1228,7 +1359,7 @@
         <v>0.80</v>
       </c>
       <c r="C6" t="str">
-        <v>0.00</v>
+        <v>0.80</v>
       </c>
     </row>
     <row r="7">
@@ -1239,7 +1370,7 @@
         <v>7.67</v>
       </c>
       <c r="C7" t="str">
-        <v>0.00</v>
+        <v>7.03</v>
       </c>
     </row>
   </sheetData>
